--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.libreoffice.org/" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc" lowestEdited="4"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -10,23 +10,19 @@
   <sheets>
     <sheet name="정보" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="정간목록" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="악보 1" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="악보 2" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="악보" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">정간목록!$A$1:$K$133</definedName>
-  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <ns2:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="127">
   <si>
     <t xml:space="preserve">각설이 타령</t>
   </si>
@@ -419,7 +415,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -448,6 +444,28 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -463,7 +481,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -476,6 +494,99 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -504,7 +615,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -524,6 +635,64 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -4988,1011 +5157,1133 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="6" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="6" customWidth="1"/>
+    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="6" customWidth="1"/>
+    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="17" max="17" width="6" customWidth="1"/>
+    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="19" max="19" width="6" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="1"/>
+    <row r="2" ht="60" hidden="false" customHeight="1">
+      <c s="6" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">각설이 타령</t>
+        </is>
+      </c>
+      <c s="6" r="C2"/>
+      <c s="6" r="D2"/>
+      <c s="6" r="E2"/>
+      <c s="6" r="F2"/>
+      <c s="6" r="G2"/>
+      <c s="6" r="H2"/>
+      <c s="6" r="I2"/>
+      <c s="6" r="J2"/>
+      <c s="6" r="K2"/>
+      <c s="6" r="L2"/>
+      <c s="6" r="M2"/>
+      <c s="6" r="N2"/>
+      <c s="6" r="O2"/>
+      <c s="6" r="P2"/>
+      <c s="6" r="Q2"/>
+      <c s="6" r="R2"/>
+      <c s="6" r="S2"/>
+      <c s="6" r="T2"/>
+      <c s="6" r="U2"/>
+    </row>
+    <row r="3" ht="56" hidden="false" customHeight="1">
+      <c r="B3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K3" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="4" t="s">
+      <c r="L3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="R3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S3" s="4" t="s">
+      <c r="R3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="T3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="T3" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U3" s="16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" ht="56" hidden="false" customHeight="1">
+      <c r="B4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="F4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="J4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K4" s="4" t="s">
+      <c r="J4" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4" t="s">
+      <c r="L4" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="17"/>
+      <c r="N4" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="O4" s="17"/>
+      <c r="P4" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4" t="s">
+      <c r="S4" s="17"/>
+      <c r="T4" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="U4" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="U4" s="17"/>
+    </row>
+    <row r="5" ht="56" hidden="false" customHeight="1">
+      <c r="B5" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="H5" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="J5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" s="4" t="s">
+      <c r="L5" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O5" s="4" t="s">
+      <c r="N5" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="18" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
+    <row r="6" ht="56" hidden="false" customHeight="1">
+      <c r="B6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" s="4" t="s">
+      <c r="L6" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O6" s="4" t="s">
+      <c r="N6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O6" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="4" t="s">
+      <c r="P6" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="R6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="S6" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="T6" s="4" t="s">
+      <c r="T6" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="U6" s="16" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
+    <row r="7" ht="56" hidden="false" customHeight="1">
+      <c r="B7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="H7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" s="4" t="s">
+      <c r="J7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M7" s="4" t="s">
+      <c r="L7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M7" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="N7" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="P7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" s="4" t="s">
+      <c r="P7" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="R7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="S7" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="T7" s="4" t="s">
+      <c r="T7" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="U7" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
+    <row r="8" ht="56" hidden="false" customHeight="1">
+      <c r="B8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="4" t="s">
+      <c r="H8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K8" s="4" t="s">
+      <c r="J8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O8" s="4" t="s">
+      <c r="M8" s="18"/>
+      <c r="N8" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="O8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S8" s="4" t="s">
+      <c r="R8" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="T8" s="4" t="s">
+      <c r="T8" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="U8" s="18" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="4" t="s">
+    <row r="9" ht="56" hidden="false" customHeight="1">
+      <c r="B9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="4" t="s">
+      <c r="H9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="4" t="s">
+      <c r="J9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="4" t="s">
+      <c r="L9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O9" s="4" t="s">
+      <c r="N9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O9" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="P9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S9" s="4" t="s">
+      <c r="P9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S9" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="T9" s="4" t="s">
+      <c r="T9" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="U9" s="16" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row r="10" ht="56" hidden="false" customHeight="1">
+      <c r="B10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="D10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M10" s="4" t="s">
+      <c r="L10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="N10" s="4" t="s">
+      <c r="N10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="O10" s="4" t="s">
+      <c r="O10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="P10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4" t="s">
+      <c r="P10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" s="17"/>
+      <c r="T10" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="U10" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="4" t="s">
+    <row r="11" ht="56" hidden="false" customHeight="1">
+      <c r="B11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="D11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="K11" s="4" t="s">
+      <c r="F11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="18"/>
+      <c r="J11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M11" s="4" t="s">
+      <c r="L11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O11" s="4" t="s">
+      <c r="N11" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="O11" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="P11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4" t="s">
+      <c r="P11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q11" s="18"/>
+      <c r="R11" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4" t="s">
+      <c r="S11" s="18"/>
+      <c r="T11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U11" s="4" t="s">
+      <c r="U11" s="18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4" t="s">
+    <row r="12" ht="56" hidden="false" customHeight="1">
+      <c r="B12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K12" s="4" t="s">
+      <c r="F12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K12" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O12" s="4" t="s">
+      <c r="L12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="M12" s="16"/>
+      <c r="N12" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O12" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="P12" s="4" t="s">
+      <c r="P12" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="U12" s="4" t="s">
+      <c r="Q12" s="16"/>
+      <c r="R12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S12" s="16"/>
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U12" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O13" s="4" t="s">
+    <row r="13" ht="56" hidden="false" customHeight="1">
+      <c r="B13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="P13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="U13" s="4" t="s">
+      <c r="P13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="17"/>
+      <c r="T13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4" t="s">
+    <row r="14" ht="56" hidden="false" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4" t="s">
+      <c r="E14" s="18"/>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
+      <c r="I14" s="18"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="O14" s="4" t="s">
+      <c r="M14" s="18"/>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O14" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="P14" s="4" t="s">
+      <c r="P14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4" t="s">
+      <c r="Q14" s="18"/>
+      <c r="R14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4" t="s">
+      <c r="S14" s="18"/>
+      <c r="T14" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="U14" s="4"/>
+      <c r="U14" s="18"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" hidden="false" customHeight="1">
+      <c s="6" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">각설이 타령</t>
+        </is>
+      </c>
+      <c s="6" r="C16"/>
+      <c s="6" r="D16"/>
+      <c s="6" r="E16"/>
+      <c s="6" r="F16"/>
+      <c s="6" r="G16"/>
+      <c s="6" r="H16"/>
+      <c s="6" r="I16"/>
+      <c s="6" r="J16"/>
+      <c s="6" r="K16"/>
+      <c s="6" r="L16"/>
+      <c s="6" r="M16"/>
+      <c s="6" r="N16"/>
+      <c s="6" r="O16"/>
+      <c s="6" r="P16"/>
+      <c s="6" r="Q16"/>
+      <c s="6" r="R16"/>
+      <c s="6" r="S16"/>
+      <c s="6" r="T16"/>
+      <c s="6" r="U16"/>
+    </row>
+    <row r="17" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B17"/>
+      <c s="19" r="C17"/>
+      <c s="15" r="D17"/>
+      <c s="19" r="E17"/>
+      <c s="15" r="F17"/>
+      <c s="19" r="G17"/>
+      <c s="15" r="H17"/>
+      <c s="19" r="I17"/>
+      <c s="15" r="J17"/>
+      <c s="19" r="K17"/>
+      <c s="15" r="L17"/>
+      <c s="19" r="M17"/>
+      <c s="15" r="N17"/>
+      <c s="19" r="O17"/>
+      <c s="15" r="P17"/>
+      <c s="19" r="Q17"/>
+      <c s="15" r="R17"/>
+      <c s="19" r="S17"/>
+      <c r="T17" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="U17" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B18"/>
+      <c s="20" r="C18"/>
+      <c s="15" r="D18"/>
+      <c s="20" r="E18"/>
+      <c s="15" r="F18"/>
+      <c s="20" r="G18"/>
+      <c s="15" r="H18"/>
+      <c s="20" r="I18"/>
+      <c s="15" r="J18"/>
+      <c s="20" r="K18"/>
+      <c s="15" r="L18"/>
+      <c s="20" r="M18"/>
+      <c s="15" r="N18"/>
+      <c s="20" r="O18"/>
+      <c s="15" r="P18"/>
+      <c s="20" r="Q18"/>
+      <c s="15" r="R18"/>
+      <c s="20" r="S18"/>
+      <c r="T18" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B19"/>
+      <c s="21" r="C19"/>
+      <c s="15" r="D19"/>
+      <c s="21" r="E19"/>
+      <c s="15" r="F19"/>
+      <c s="21" r="G19"/>
+      <c s="15" r="H19"/>
+      <c s="21" r="I19"/>
+      <c s="15" r="J19"/>
+      <c s="21" r="K19"/>
+      <c s="15" r="L19"/>
+      <c s="21" r="M19"/>
+      <c s="15" r="N19"/>
+      <c s="21" r="O19"/>
+      <c s="15" r="P19"/>
+      <c s="21" r="Q19"/>
+      <c s="15" r="R19"/>
+      <c s="21" r="S19"/>
+      <c r="T19" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="U19" s="18" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B20"/>
+      <c s="19" r="C20"/>
+      <c s="15" r="D20"/>
+      <c s="19" r="E20"/>
+      <c s="15" r="F20"/>
+      <c s="19" r="G20"/>
+      <c s="15" r="H20"/>
+      <c s="19" r="I20"/>
+      <c s="15" r="J20"/>
+      <c s="19" r="K20"/>
+      <c s="15" r="L20"/>
+      <c s="19" r="M20"/>
+      <c s="15" r="N20"/>
+      <c s="19" r="O20"/>
+      <c s="15" r="P20"/>
+      <c s="19" r="Q20"/>
+      <c s="15" r="R20"/>
+      <c s="19" r="S20"/>
+      <c r="T20" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U20" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="21" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B21"/>
+      <c s="20" r="C21"/>
+      <c s="15" r="D21"/>
+      <c s="20" r="E21"/>
+      <c s="15" r="F21"/>
+      <c s="20" r="G21"/>
+      <c s="15" r="H21"/>
+      <c s="20" r="I21"/>
+      <c s="15" r="J21"/>
+      <c s="20" r="K21"/>
+      <c s="15" r="L21"/>
+      <c s="20" r="M21"/>
+      <c s="15" r="N21"/>
+      <c s="20" r="O21"/>
+      <c s="15" r="P21"/>
+      <c s="20" r="Q21"/>
+      <c s="15" r="R21"/>
+      <c s="20" r="S21"/>
+      <c r="T21" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U21" s="17" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B22"/>
+      <c s="21" r="C22"/>
+      <c s="15" r="D22"/>
+      <c s="21" r="E22"/>
+      <c s="15" r="F22"/>
+      <c s="21" r="G22"/>
+      <c s="15" r="H22"/>
+      <c s="21" r="I22"/>
+      <c s="15" r="J22"/>
+      <c s="21" r="K22"/>
+      <c s="15" r="L22"/>
+      <c s="21" r="M22"/>
+      <c s="15" r="N22"/>
+      <c s="21" r="O22"/>
+      <c s="15" r="P22"/>
+      <c s="21" r="Q22"/>
+      <c s="15" r="R22"/>
+      <c s="21" r="S22"/>
+      <c r="T22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="U22" s="18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="23" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B23"/>
+      <c s="19" r="C23"/>
+      <c s="15" r="D23"/>
+      <c s="19" r="E23"/>
+      <c s="15" r="F23"/>
+      <c s="19" r="G23"/>
+      <c s="15" r="H23"/>
+      <c s="19" r="I23"/>
+      <c s="15" r="J23"/>
+      <c s="19" r="K23"/>
+      <c s="15" r="L23"/>
+      <c s="19" r="M23"/>
+      <c s="15" r="N23"/>
+      <c s="19" r="O23"/>
+      <c s="15" r="P23"/>
+      <c s="19" r="Q23"/>
+      <c s="15" r="R23"/>
+      <c s="19" r="S23"/>
+      <c r="T23" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U23" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B24"/>
+      <c s="20" r="C24"/>
+      <c s="15" r="D24"/>
+      <c s="20" r="E24"/>
+      <c s="15" r="F24"/>
+      <c s="20" r="G24"/>
+      <c s="15" r="H24"/>
+      <c s="20" r="I24"/>
+      <c s="15" r="J24"/>
+      <c s="20" r="K24"/>
+      <c s="15" r="L24"/>
+      <c s="20" r="M24"/>
+      <c s="15" r="N24"/>
+      <c s="20" r="O24"/>
+      <c s="15" r="P24"/>
+      <c s="20" r="Q24"/>
+      <c s="15" r="R24"/>
+      <c s="20" r="S24"/>
+      <c r="T24" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="U24" s="17" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B25"/>
+      <c s="21" r="C25"/>
+      <c s="15" r="D25"/>
+      <c s="21" r="E25"/>
+      <c s="15" r="F25"/>
+      <c s="21" r="G25"/>
+      <c s="15" r="H25"/>
+      <c s="21" r="I25"/>
+      <c s="15" r="J25"/>
+      <c s="21" r="K25"/>
+      <c s="15" r="L25"/>
+      <c s="21" r="M25"/>
+      <c s="15" r="N25"/>
+      <c s="21" r="O25"/>
+      <c s="15" r="P25"/>
+      <c s="21" r="Q25"/>
+      <c s="15" r="R25"/>
+      <c s="21" r="S25"/>
+      <c r="T25" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="U25" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B26"/>
+      <c s="19" r="C26"/>
+      <c s="15" r="D26"/>
+      <c s="19" r="E26"/>
+      <c s="15" r="F26"/>
+      <c s="19" r="G26"/>
+      <c s="15" r="H26"/>
+      <c s="19" r="I26"/>
+      <c s="15" r="J26"/>
+      <c s="19" r="K26"/>
+      <c s="15" r="L26"/>
+      <c s="19" r="M26"/>
+      <c s="15" r="N26"/>
+      <c s="19" r="O26"/>
+      <c s="15" r="P26"/>
+      <c s="19" r="Q26"/>
+      <c s="15" r="R26"/>
+      <c s="19" r="S26"/>
+      <c r="T26" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U26" s="16"/>
+    </row>
+    <row r="27" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B27"/>
+      <c s="20" r="C27"/>
+      <c s="15" r="D27"/>
+      <c s="20" r="E27"/>
+      <c s="15" r="F27"/>
+      <c s="20" r="G27"/>
+      <c s="15" r="H27"/>
+      <c s="20" r="I27"/>
+      <c s="15" r="J27"/>
+      <c s="20" r="K27"/>
+      <c s="15" r="L27"/>
+      <c s="20" r="M27"/>
+      <c s="15" r="N27"/>
+      <c s="20" r="O27"/>
+      <c s="15" r="P27"/>
+      <c s="20" r="Q27"/>
+      <c s="15" r="R27"/>
+      <c s="20" r="S27"/>
+      <c r="T27" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="U27" s="17"/>
+    </row>
+    <row r="28" ht="56" hidden="false" customHeight="1">
+      <c s="15" r="B28"/>
+      <c s="21" r="C28"/>
+      <c s="15" r="D28"/>
+      <c s="21" r="E28"/>
+      <c s="15" r="F28"/>
+      <c s="21" r="G28"/>
+      <c s="15" r="H28"/>
+      <c s="21" r="I28"/>
+      <c s="15" r="J28"/>
+      <c s="21" r="K28"/>
+      <c s="15" r="L28"/>
+      <c s="21" r="M28"/>
+      <c s="15" r="N28"/>
+      <c s="21" r="O28"/>
+      <c s="15" r="P28"/>
+      <c s="21" r="Q28"/>
+      <c s="15" r="R28"/>
+      <c s="21" r="S28"/>
+      <c r="T28" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="U28" s="18"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultColWidth="8.50390625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="4"/>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="4"/>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">기호</t>
   </si>
   <si>
-    <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+    <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
   </si>
   <si>
     <t xml:space="preserve">노란 칸</t>
@@ -220,10 +220,10 @@
 㴌</t>
   </si>
   <si>
-    <t xml:space="preserve">―|㴌</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|㴌</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 㴌</t>
   </si>
   <si>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">겠네</t>
   </si>
   <si>
-    <t xml:space="preserve">―</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―|△⌞</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–|△⌞</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 △⌞</t>
   </si>
   <si>
@@ -369,17 +369,17 @@
     <t xml:space="preserve">모아</t>
   </si>
   <si>
-    <t xml:space="preserve">―|―</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
-―</t>
+    <t xml:space="preserve">–|–</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
+–</t>
   </si>
   <si>
     <t xml:space="preserve">짧은 가로선 두 개</t>
   </si>
   <si>
-    <t xml:space="preserve">왼쪽 아래 L자 표시, 위 짧은 획 ―로 적음</t>
+    <t xml:space="preserve">왼쪽 아래 L자 표시, 위 짧은 획 –로 적음</t>
   </si>
   <si>
     <t xml:space="preserve">湳</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">주</t>
   </si>
   <si>
-    <t xml:space="preserve">―|△</t>
-  </si>
-  <si>
-    <t xml:space="preserve">―
+    <t xml:space="preserve">–|△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–
 △</t>
   </si>
   <si>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -548,45 +548,64 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="24"/>
+      <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -681,7 +700,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -739,6 +758,50 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5157,808 +5220,808 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
     </row>
     <row r="3" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="O4" s="11" t="s">
+      <c r="O4" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="11" t="s">
+      <c r="Q4" s="22" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="11" t="s">
+      <c r="I5" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="22" t="s">
         <v>100</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="11" t="s">
+      <c r="O5" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="11" t="s">
+      <c r="Q5" s="22" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="K6" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="M6" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O6" s="13" t="s">
+      <c r="O6" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Q6" s="13" t="s">
+      <c r="Q6" s="24" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="19" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I8" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q8" s="11" t="s">
+      <c r="Q8" s="22" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="22"/>
+      <c r="D9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="22"/>
+      <c r="F9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="7" t="s">
+      <c r="K9" s="22"/>
+      <c r="L9" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="O9" s="11"/>
-      <c r="P9" s="7" t="s">
+      <c r="O9" s="22"/>
+      <c r="P9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="11" t="s">
+      <c r="Q9" s="22" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="24"/>
+      <c r="D10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="24"/>
+      <c r="F10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="K10" s="14"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="25"/>
+      <c r="L10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="M10" s="13" t="s">
+      <c r="M10" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="N10" s="9" t="s">
+      <c r="N10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="25"/>
+      <c r="P10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="13" t="s">
+      <c r="Q10" s="24" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="P11" s="7" t="s">
+      <c r="P11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="19" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="9" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="P12" s="7" t="s">
+      <c r="P12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="Q12" s="11" t="s">
+      <c r="Q12" s="22" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="11" t="s">
+      <c r="I13" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="11" t="s">
+      <c r="K13" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="11" t="s">
+      <c r="M13" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="P13" s="7" t="s">
+      <c r="P13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="Q13" s="11" t="s">
+      <c r="Q13" s="22" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="13" t="s">
+      <c r="I14" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="M14" s="24" t="s">
         <v>107</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="13" t="s">
+      <c r="O14" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="P14" s="7" t="s">
+      <c r="P14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="Q14" s="13" t="s">
+      <c r="Q14" s="24" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="7" t="s">
+      <c r="J15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="L15" s="7" t="s">
+      <c r="L15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="M15" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="N15" s="7" t="s">
+      <c r="N15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="P15" s="7" t="s">
+      <c r="P15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="Q15" s="19" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="11" t="s">
+      <c r="I16" s="22" t="s">
         <v>122</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="J16" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="7" t="s">
+      <c r="L16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="M16" s="11" t="s">
+      <c r="M16" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="N16" s="7" t="s">
+      <c r="N16" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O16" s="11" t="s">
+      <c r="O16" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="P16" s="7" t="s">
+      <c r="P16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="Q16" s="22" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="7" t="s">
+      <c r="C17" s="22"/>
+      <c r="D17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="7" t="s">
+      <c r="E17" s="22"/>
+      <c r="F17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="22"/>
+      <c r="J17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="M17" s="12"/>
-      <c r="N17" s="7" t="s">
+      <c r="M17" s="23"/>
+      <c r="N17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="O17" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="P17" s="7" t="s">
+      <c r="P17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="Q17" s="22" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="24"/>
+      <c r="D18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="7" t="s">
+      <c r="E18" s="24"/>
+      <c r="F18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="24"/>
+      <c r="J18" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="M18" s="14"/>
-      <c r="N18" s="7" t="s">
+      <c r="M18" s="25"/>
+      <c r="N18" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O18" s="13" t="s">
+      <c r="O18" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="P18" s="7" t="s">
+      <c r="P18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="Q18" s="13" t="s">
+      <c r="Q18" s="24" t="s">
         <v>80</v>
       </c>
     </row>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -5220,26 +5220,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -5259,7 +5259,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
@@ -5309,7 +5309,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="18" t="s">
         <v>48</v>
       </c>
@@ -5459,7 +5459,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
@@ -5509,7 +5509,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
@@ -5601,7 +5601,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="18" t="s">
         <v>132</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="18" t="s">
         <v>162</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="18" t="s">
         <v>92</v>
       </c>
@@ -5741,7 +5741,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
@@ -5791,7 +5791,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="18" t="s">
         <v>119</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="18" t="s">
         <v>87</v>
       </c>
@@ -5891,7 +5891,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="20" t="s">
         <v>90</v>
       </c>
@@ -5941,7 +5941,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="18" t="s">
         <v>92</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="56" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="18" t="s">
         <v>132</v>
       </c>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="192">
   <si>
     <t xml:space="preserve">각설이 타령</t>
   </si>
@@ -539,6 +539,110 @@
   </si>
   <si>
     <t xml:space="preserve">가사 한다/논다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">았
+네</t>
+  </si>
+  <si>
+    <t xml:space="preserve">으
+면</t>
+  </si>
+  <si>
+    <t xml:space="preserve">자
+나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">파
+가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">이
+가</t>
+  </si>
+  <si>
+    <t xml:space="preserve">었
+지</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장
+을</t>
+  </si>
+  <si>
+    <t xml:space="preserve">잘
+도</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가
+는</t>
+  </si>
+  <si>
+    <t xml:space="preserve">좋
+을</t>
+  </si>
+  <si>
+    <t xml:space="preserve">못
+잊</t>
+  </si>
+  <si>
+    <t xml:space="preserve">논
+다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">길
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">시
+구</t>
+  </si>
+  <si>
+    <t xml:space="preserve">겠
+네</t>
+  </si>
+  <si>
+    <t xml:space="preserve">고
+나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">네
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">헤
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">어
+허</t>
+  </si>
+  <si>
+    <t xml:space="preserve">섯
+에</t>
+  </si>
+  <si>
+    <t xml:space="preserve">장
+이</t>
+  </si>
+  <si>
+    <t xml:space="preserve">만
+났</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한
+테</t>
+  </si>
+  <si>
+    <t xml:space="preserve">한
+다</t>
+  </si>
+  <si>
+    <t xml:space="preserve">구
+나</t>
+  </si>
+  <si>
+    <t xml:space="preserve">모
+아</t>
   </si>
 </sst>
 </file>
@@ -5326,7 +5430,7 @@
         <v>48</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>64</v>
@@ -5350,13 +5454,13 @@
         <v>83</v>
       </c>
       <c r="O4" s="22" t="s">
-        <v>84</v>
+        <v>167</v>
       </c>
       <c r="P4" s="18" t="s">
         <v>48</v>
       </c>
       <c r="Q4" s="22" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5414,7 +5518,7 @@
         <v>48</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>48</v>
@@ -5426,7 +5530,7 @@
         <v>48</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>69</v>
@@ -5438,7 +5542,7 @@
         <v>119</v>
       </c>
       <c r="K6" s="24" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="L6" s="18" t="s">
         <v>69</v>
@@ -5450,13 +5554,13 @@
         <v>48</v>
       </c>
       <c r="O6" s="24" t="s">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="P6" s="18" t="s">
         <v>48</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>52</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5464,13 +5568,13 @@
         <v>87</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>87</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>146</v>
+        <v>174</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>45</v>
@@ -5488,7 +5592,7 @@
         <v>87</v>
       </c>
       <c r="K7" s="19" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="L7" s="18" t="s">
         <v>71</v>
@@ -5500,7 +5604,7 @@
         <v>87</v>
       </c>
       <c r="O7" s="19" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="P7" s="18" t="s">
         <v>45</v>
@@ -5514,13 +5618,13 @@
         <v>90</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>90</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>55</v>
@@ -5538,7 +5642,7 @@
         <v>90</v>
       </c>
       <c r="K8" s="22" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="L8" s="18" t="s">
         <v>74</v>
@@ -5550,13 +5654,13 @@
         <v>90</v>
       </c>
       <c r="O8" s="22" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="P8" s="18" t="s">
         <v>55</v>
       </c>
       <c r="Q8" s="22" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5572,7 +5676,7 @@
         <v>58</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>76</v>
@@ -5614,7 +5718,7 @@
         <v>55</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>137</v>
+        <v>183</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>79</v>
@@ -5648,7 +5752,7 @@
         <v>162</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>114</v>
@@ -5720,7 +5824,7 @@
         <v>48</v>
       </c>
       <c r="K12" s="22" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="L12" s="18" t="s">
         <v>83</v>
@@ -5732,7 +5836,7 @@
         <v>48</v>
       </c>
       <c r="O12" s="22" t="s">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="P12" s="18" t="s">
         <v>64</v>
@@ -5796,7 +5900,7 @@
         <v>119</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>119</v>
@@ -5808,19 +5912,19 @@
         <v>69</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>140</v>
+        <v>186</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>48</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>48</v>
       </c>
       <c r="K14" s="24" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="L14" s="18" t="s">
         <v>45</v>
@@ -5832,7 +5936,7 @@
         <v>48</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="P14" s="18" t="s">
         <v>69</v>
@@ -5846,13 +5950,13 @@
         <v>87</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>87</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>71</v>
@@ -5864,7 +5968,7 @@
         <v>87</v>
       </c>
       <c r="I15" s="19" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>45</v>
@@ -5876,7 +5980,7 @@
         <v>87</v>
       </c>
       <c r="M15" s="19" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="N15" s="18" t="s">
         <v>45</v>
@@ -5896,13 +6000,13 @@
         <v>90</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>90</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>74</v>
@@ -5914,25 +6018,25 @@
         <v>90</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>55</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="L16" s="18" t="s">
         <v>90</v>
       </c>
       <c r="M16" s="22" t="s">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="N16" s="18" t="s">
         <v>55</v>
       </c>
       <c r="O16" s="22" t="s">
-        <v>56</v>
+        <v>181</v>
       </c>
       <c r="P16" s="18" t="s">
         <v>74</v>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -652,7 +652,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -709,6 +709,12 @@
     <font>
       <b val="true"/>
       <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
       <charset val="1"/>
@@ -804,7 +810,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="33">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -906,6 +912,34 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5325,21 +5359,21 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="26" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="16" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="26" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -5367,49 +5401,49 @@
       <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="27" t="s">
         <v>155</v>
       </c>
       <c r="D3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="27" t="s">
         <v>138</v>
       </c>
       <c r="F3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="27" t="s">
         <v>133</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="21" t="s">
+      <c r="I3" s="28" t="s">
         <v>125</v>
       </c>
       <c r="J3" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="27" t="s">
         <v>115</v>
       </c>
       <c r="L3" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="M3" s="19" t="s">
+      <c r="M3" s="27" t="s">
         <v>98</v>
       </c>
       <c r="N3" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="27" t="s">
         <v>81</v>
       </c>
       <c r="P3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="19" t="s">
+      <c r="Q3" s="27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5417,49 +5451,49 @@
       <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="29" t="s">
         <v>156</v>
       </c>
       <c r="D4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="29" t="s">
         <v>143</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="29" t="s">
         <v>166</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I4" s="22" t="s">
+      <c r="I4" s="29" t="s">
         <v>99</v>
       </c>
       <c r="J4" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="29" t="s">
         <v>116</v>
       </c>
       <c r="L4" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="29" t="s">
         <v>99</v>
       </c>
       <c r="N4" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="O4" s="22" t="s">
+      <c r="O4" s="29" t="s">
         <v>167</v>
       </c>
       <c r="P4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="22" t="s">
+      <c r="Q4" s="29" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5467,49 +5501,49 @@
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="29" t="s">
         <v>157</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E5" s="30" t="s">
         <v>144</v>
       </c>
       <c r="F5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="29" t="s">
         <v>133</v>
       </c>
       <c r="H5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I5" s="22" t="s">
+      <c r="I5" s="29" t="s">
         <v>100</v>
       </c>
       <c r="J5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K5" s="22" t="s">
+      <c r="K5" s="29" t="s">
         <v>117</v>
       </c>
       <c r="L5" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="29" t="s">
         <v>100</v>
       </c>
       <c r="N5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="29" t="s">
         <v>81</v>
       </c>
       <c r="P5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="29" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5517,49 +5551,49 @@
       <c r="B6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="31" t="s">
         <v>169</v>
       </c>
       <c r="D6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="31" t="s">
         <v>143</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="31" t="s">
         <v>166</v>
       </c>
       <c r="H6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I6" s="24" t="s">
+      <c r="I6" s="31" t="s">
         <v>101</v>
       </c>
       <c r="J6" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="31" t="s">
         <v>170</v>
       </c>
       <c r="L6" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="M6" s="24" t="s">
+      <c r="M6" s="31" t="s">
         <v>101</v>
       </c>
       <c r="N6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O6" s="24" t="s">
+      <c r="O6" s="31" t="s">
         <v>171</v>
       </c>
       <c r="P6" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Q6" s="24" t="s">
+      <c r="Q6" s="31" t="s">
         <v>172</v>
       </c>
     </row>
@@ -5567,49 +5601,49 @@
       <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="27" t="s">
         <v>173</v>
       </c>
       <c r="D7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="27" t="s">
         <v>174</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="27" t="s">
         <v>133</v>
       </c>
       <c r="H7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="27" t="s">
         <v>125</v>
       </c>
       <c r="J7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="27" t="s">
         <v>175</v>
       </c>
       <c r="L7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="27" t="s">
         <v>67</v>
       </c>
       <c r="N7" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="O7" s="19" t="s">
+      <c r="O7" s="27" t="s">
         <v>176</v>
       </c>
       <c r="P7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="19" t="s">
+      <c r="Q7" s="27" t="s">
         <v>53</v>
       </c>
     </row>
@@ -5617,49 +5651,49 @@
       <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="29" t="s">
         <v>177</v>
       </c>
       <c r="D8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="29" t="s">
         <v>178</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="29" t="s">
         <v>135</v>
       </c>
       <c r="H8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="29" t="s">
         <v>127</v>
       </c>
       <c r="J8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="K8" s="22" t="s">
+      <c r="K8" s="29" t="s">
         <v>179</v>
       </c>
       <c r="L8" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="M8" s="22" t="s">
+      <c r="M8" s="29" t="s">
         <v>98</v>
       </c>
       <c r="N8" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="O8" s="22" t="s">
+      <c r="O8" s="29" t="s">
         <v>180</v>
       </c>
       <c r="P8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q8" s="22" t="s">
+      <c r="Q8" s="29" t="s">
         <v>181</v>
       </c>
     </row>
@@ -5667,41 +5701,41 @@
       <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="29"/>
       <c r="D9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="29" t="s">
         <v>182</v>
       </c>
       <c r="H9" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="29" t="s">
         <v>102</v>
       </c>
       <c r="J9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="K9" s="22"/>
+      <c r="K9" s="29"/>
       <c r="L9" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="M9" s="22" t="s">
+      <c r="M9" s="29" t="s">
         <v>102</v>
       </c>
       <c r="N9" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="O9" s="22"/>
+      <c r="O9" s="29"/>
       <c r="P9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="22" t="s">
+      <c r="Q9" s="29" t="s">
         <v>59</v>
       </c>
     </row>
@@ -5709,41 +5743,41 @@
       <c r="B10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="24"/>
+      <c r="C10" s="31"/>
       <c r="D10" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="24"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="24" t="s">
+      <c r="G10" s="31" t="s">
         <v>183</v>
       </c>
       <c r="H10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="31" t="s">
         <v>103</v>
       </c>
       <c r="J10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="K10" s="25"/>
+      <c r="K10" s="32"/>
       <c r="L10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="M10" s="24" t="s">
+      <c r="M10" s="31" t="s">
         <v>103</v>
       </c>
       <c r="N10" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="32"/>
       <c r="P10" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="Q10" s="24" t="s">
+      <c r="Q10" s="31" t="s">
         <v>60</v>
       </c>
     </row>
@@ -5751,49 +5785,49 @@
       <c r="B11" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="27" t="s">
         <v>184</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="27" t="s">
         <v>148</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="27" t="s">
         <v>138</v>
       </c>
       <c r="H11" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="28" t="s">
         <v>128</v>
       </c>
       <c r="J11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K11" s="19" t="s">
+      <c r="K11" s="27" t="s">
         <v>123</v>
       </c>
       <c r="L11" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="M11" s="19" t="s">
+      <c r="M11" s="27" t="s">
         <v>104</v>
       </c>
       <c r="N11" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="19" t="s">
+      <c r="O11" s="27" t="s">
         <v>96</v>
       </c>
       <c r="P11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Q11" s="19" t="s">
+      <c r="Q11" s="27" t="s">
         <v>46</v>
       </c>
     </row>
@@ -5801,47 +5835,47 @@
       <c r="B12" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="30" t="s">
         <v>149</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="29" t="s">
         <v>139</v>
       </c>
       <c r="H12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="29" t="s">
         <v>130</v>
       </c>
       <c r="J12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="22" t="s">
+      <c r="K12" s="29" t="s">
         <v>185</v>
       </c>
       <c r="L12" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="M12" s="22" t="s">
+      <c r="M12" s="29" t="s">
         <v>105</v>
       </c>
       <c r="N12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O12" s="22" t="s">
+      <c r="O12" s="29" t="s">
         <v>185</v>
       </c>
       <c r="P12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="Q12" s="22" t="s">
+      <c r="Q12" s="29" t="s">
         <v>65</v>
       </c>
     </row>
@@ -5849,49 +5883,49 @@
       <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="29" t="s">
         <v>157</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="29" t="s">
         <v>151</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="29" t="s">
         <v>51</v>
       </c>
       <c r="H13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="29" t="s">
         <v>117</v>
       </c>
       <c r="J13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K13" s="22" t="s">
+      <c r="K13" s="29" t="s">
         <v>124</v>
       </c>
       <c r="L13" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="29" t="s">
         <v>106</v>
       </c>
       <c r="N13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="22" t="s">
+      <c r="O13" s="29" t="s">
         <v>98</v>
       </c>
       <c r="P13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="Q13" s="22" t="s">
+      <c r="Q13" s="29" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5899,49 +5933,49 @@
       <c r="B14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="31" t="s">
         <v>169</v>
       </c>
       <c r="D14" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="31" t="s">
         <v>152</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="24" t="s">
+      <c r="G14" s="31" t="s">
         <v>186</v>
       </c>
       <c r="H14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I14" s="24" t="s">
+      <c r="I14" s="31" t="s">
         <v>170</v>
       </c>
       <c r="J14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="31" t="s">
         <v>168</v>
       </c>
       <c r="L14" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="M14" s="24" t="s">
+      <c r="M14" s="31" t="s">
         <v>107</v>
       </c>
       <c r="N14" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="O14" s="24" t="s">
+      <c r="O14" s="31" t="s">
         <v>168</v>
       </c>
       <c r="P14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="Q14" s="24" t="s">
+      <c r="Q14" s="31" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5949,49 +5983,49 @@
       <c r="B15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="27" t="s">
         <v>173</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="27" t="s">
         <v>187</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="27" t="s">
         <v>133</v>
       </c>
       <c r="H15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="I15" s="19" t="s">
+      <c r="I15" s="27" t="s">
         <v>175</v>
       </c>
       <c r="J15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="19" t="s">
+      <c r="K15" s="27" t="s">
         <v>53</v>
       </c>
       <c r="L15" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="27" t="s">
         <v>188</v>
       </c>
       <c r="N15" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="O15" s="19" t="s">
+      <c r="O15" s="27" t="s">
         <v>53</v>
       </c>
       <c r="P15" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="Q15" s="19" t="s">
+      <c r="Q15" s="27" t="s">
         <v>72</v>
       </c>
     </row>
@@ -5999,49 +6033,49 @@
       <c r="B16" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="30" t="s">
         <v>189</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="29" t="s">
         <v>190</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="29" t="s">
         <v>135</v>
       </c>
       <c r="H16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="I16" s="22" t="s">
+      <c r="I16" s="29" t="s">
         <v>179</v>
       </c>
       <c r="J16" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="22" t="s">
+      <c r="K16" s="29" t="s">
         <v>181</v>
       </c>
       <c r="L16" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="M16" s="22" t="s">
+      <c r="M16" s="29" t="s">
         <v>191</v>
       </c>
       <c r="N16" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O16" s="22" t="s">
+      <c r="O16" s="29" t="s">
         <v>181</v>
       </c>
       <c r="P16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="Q16" s="22" t="s">
+      <c r="Q16" s="29" t="s">
         <v>75</v>
       </c>
     </row>
@@ -6049,41 +6083,41 @@
       <c r="B17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="29"/>
       <c r="D17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="29" t="s">
         <v>141</v>
       </c>
       <c r="H17" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="22"/>
+      <c r="I17" s="29"/>
       <c r="J17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="K17" s="22" t="s">
+      <c r="K17" s="29" t="s">
         <v>59</v>
       </c>
       <c r="L17" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="M17" s="23"/>
+      <c r="M17" s="30"/>
       <c r="N17" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="O17" s="22" t="s">
+      <c r="O17" s="29" t="s">
         <v>59</v>
       </c>
       <c r="P17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="Q17" s="22" t="s">
+      <c r="Q17" s="29" t="s">
         <v>77</v>
       </c>
     </row>
@@ -6091,41 +6125,41 @@
       <c r="B18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="31"/>
       <c r="D18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="E18" s="24"/>
+      <c r="E18" s="31"/>
       <c r="F18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="24" t="s">
+      <c r="G18" s="31" t="s">
         <v>142</v>
       </c>
       <c r="H18" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="I18" s="24"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="31" t="s">
         <v>60</v>
       </c>
       <c r="L18" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="M18" s="25"/>
+      <c r="M18" s="32"/>
       <c r="N18" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O18" s="24" t="s">
+      <c r="O18" s="31" t="s">
         <v>60</v>
       </c>
       <c r="P18" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="Q18" s="24" t="s">
+      <c r="Q18" s="31" t="s">
         <v>80</v>
       </c>
     </row>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -734,10 +734,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -5349,7 +5349,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:Q18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -5373,8 +5373,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="26" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>48</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>132</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>162</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>92</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>119</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B15" s="18" t="s">
         <v>87</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B16" s="20" t="s">
         <v>90</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B17" s="18" t="s">
         <v>92</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="55.19" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
       <c r="B18" s="18" t="s">
         <v>132</v>
       </c>
@@ -6166,7 +6166,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="76" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/각설이 타령.xlsx
+++ b/sheets/민요/검수/각설이 타령.xlsx
@@ -5355,26 +5355,26 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="26" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="15" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="26" width="6"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="64.52" customHeight="true">
       <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
@@ -5394,7 +5394,7 @@
       <c r="P2" s="17"/>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B3" s="18" t="s">
         <v>71</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B4" s="18" t="s">
         <v>83</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
@@ -5544,7 +5544,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B6" s="18" t="s">
         <v>48</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B7" s="18" t="s">
         <v>87</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B9" s="18" t="s">
         <v>92</v>
       </c>
@@ -5736,7 +5736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B10" s="18" t="s">
         <v>132</v>
       </c>
@@ -5778,7 +5778,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B11" s="18" t="s">
         <v>162</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B12" s="18" t="s">
         <v>92</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B13" s="18" t="s">
         <v>45</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B14" s="18" t="s">
         <v>119</v>
       </c>
@@ -5976,7 +5976,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B15" s="18" t="s">
         <v>87</v>
       </c>
@@ -6026,7 +6026,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B16" s="20" t="s">
         <v>90</v>
       </c>
@@ -6076,7 +6076,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B17" s="18" t="s">
         <v>92</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="72.04" customHeight="true">
       <c r="B18" s="18" t="s">
         <v>132</v>
       </c>
@@ -6166,7 +6166,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
